--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ADF4676-9AAB-4D37-BF3A-B1C34B85C37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0B07F7-2DB0-4068-866D-155E65D5FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -31,6 +31,161 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
+  <si>
+    <t>register</t>
+  </si>
+  <si>
+    <t>english</t>
+  </si>
+  <si>
+    <t>french</t>
+  </si>
+  <si>
+    <t>Je t'kiffe.</t>
+  </si>
+  <si>
+    <t>Je tiens énormément à toi.</t>
+  </si>
+  <si>
+    <t>Je t'aime.</t>
+  </si>
+  <si>
+    <t>Je vous aime profondément.</t>
+  </si>
+  <si>
+    <t>Veuillez recevoir l'expression de mon profond attachement.</t>
+  </si>
+  <si>
+    <t>I love you.</t>
+  </si>
+  <si>
+    <t>STREET</t>
+  </si>
+  <si>
+    <t>CONVERSATIONAL</t>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>FORMAL</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE</t>
+  </si>
+  <si>
+    <t>Do you have any suggestions ?</t>
+  </si>
+  <si>
+    <t>T'as des idées ?</t>
+  </si>
+  <si>
+    <t>Tu aurais une suggestion ?</t>
+  </si>
+  <si>
+    <t>As-tu des suggestions ?</t>
+  </si>
+  <si>
+    <t>Auriez-vous des suggestions ?</t>
+  </si>
+  <si>
+    <t>Auriez-vous des recommandations à formuler ?</t>
+  </si>
+  <si>
+    <t>You weren't supposed to know.</t>
+  </si>
+  <si>
+    <t>Tu n'étais pas censé le savoir.</t>
+  </si>
+  <si>
+    <t>Vous n'étiez pas censé le savoir.</t>
+  </si>
+  <si>
+    <t>Vous n'étiez pas censé avoir connaissance de cette information.</t>
+  </si>
+  <si>
+    <t>T'étais pas censé capter ça.</t>
+  </si>
+  <si>
+    <t>Tu n'aurais jamais dû apprendre ça.</t>
+  </si>
+  <si>
+    <t>That's not gonna work.</t>
+  </si>
+  <si>
+    <t>Ça va pas le faire.</t>
+  </si>
+  <si>
+    <t>Ça marchera pas.</t>
+  </si>
+  <si>
+    <t>Ça ne marchera pas.</t>
+  </si>
+  <si>
+    <t>Cela ne fonctionnera pas.</t>
+  </si>
+  <si>
+    <t>Cette solution n'est pas envisageable.</t>
+  </si>
+  <si>
+    <t>I need some help.</t>
+  </si>
+  <si>
+    <t>J'ai besoin d'un coup de main.</t>
+  </si>
+  <si>
+    <t>J'ai besoin d'un peu d'aide.</t>
+  </si>
+  <si>
+    <t>J'ai besoin d'aide.</t>
+  </si>
+  <si>
+    <t>J'aurais besoin de votre aide.</t>
+  </si>
+  <si>
+    <t>Je requiers une assistance.</t>
+  </si>
+  <si>
+    <t>Ça fait un bail.</t>
+  </si>
+  <si>
+    <t>Ça fait un moment.</t>
+  </si>
+  <si>
+    <t>Ça fait longtemps.</t>
+  </si>
+  <si>
+    <t>Une longue période s'est écoulée depuis notre dernier échange.</t>
+  </si>
+  <si>
+    <t>Cela fait longtemps que nous ne nous sommes pas vus.</t>
+  </si>
+  <si>
+    <t>It's been a long time.</t>
+  </si>
+  <si>
+    <t>I can't believe he did that.</t>
+  </si>
+  <si>
+    <t>Je bugue grave qu'il ait fait ça.</t>
+  </si>
+  <si>
+    <t>Il est difficile de croire qu'il ait agi de cette manière.</t>
+  </si>
+  <si>
+    <t>Je suis stupéfait qu'il ait fait cela.</t>
+  </si>
+  <si>
+    <t>Je n'arrive pas à croire qu'il ait fait ça.</t>
+  </si>
+  <si>
+    <t>J'en reviens pas qu'il ait fait ça.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,9 +535,411 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" customWidth="1"/>
+    <col min="3" max="3" width="55.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0B07F7-2DB0-4068-866D-155E65D5FF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D98F229-3BEE-4FF7-9C15-8EA461696008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>register</t>
   </si>
@@ -184,6 +184,132 @@
   </si>
   <si>
     <t>J'en reviens pas qu'il ait fait ça.</t>
+  </si>
+  <si>
+    <t>Shut up.</t>
+  </si>
+  <si>
+    <t>Ta gueule.</t>
+  </si>
+  <si>
+    <t>La ferme.</t>
+  </si>
+  <si>
+    <t>Tais-toi.</t>
+  </si>
+  <si>
+    <t>Veuillez vous taire.</t>
+  </si>
+  <si>
+    <t>Je vous prie de bien vouloir garder le silence.</t>
+  </si>
+  <si>
+    <t>Au nom de quoi vous permettez-vous d'agir ainsi ?</t>
+  </si>
+  <si>
+    <t>Mais t'es qui, toi ?</t>
+  </si>
+  <si>
+    <t>Pour qui vous prenez-vous ?</t>
+  </si>
+  <si>
+    <t>Pour qui tu te prends ?</t>
+  </si>
+  <si>
+    <t>Pour qui te prends-tu ?</t>
+  </si>
+  <si>
+    <t>Who do you think you are ?</t>
+  </si>
+  <si>
+    <t>I agree.</t>
+  </si>
+  <si>
+    <t>Je partage votre avis.</t>
+  </si>
+  <si>
+    <t>J'exprime mon accord.</t>
+  </si>
+  <si>
+    <t>Je suis d'accord.</t>
+  </si>
+  <si>
+    <t>Tout à fait d'accord.</t>
+  </si>
+  <si>
+    <t>Grave.</t>
+  </si>
+  <si>
+    <t>Avez-vous eu l'occasion de vous rendre au restaurant que je vous avais recommandé ?</t>
+  </si>
+  <si>
+    <t>Êtes-vous allé au restaurant dont je vous ai parlé ?</t>
+  </si>
+  <si>
+    <t>Tu es allé au restaurant dont je t'ai parlé ?</t>
+  </si>
+  <si>
+    <t>Alors, t'es allé au resto dont je t'ai parlé ?</t>
+  </si>
+  <si>
+    <t>Du coup, t'as testé le resto ?</t>
+  </si>
+  <si>
+    <t>Did you go to the restaurant I told you about ?</t>
+  </si>
+  <si>
+    <t>Comment avez-vous pu nous infliger une telle situation ?</t>
+  </si>
+  <si>
+    <t>Comment avez-vous pu nous faire cela ?</t>
+  </si>
+  <si>
+    <t>Comment as-tu pu nous faire ça ?</t>
+  </si>
+  <si>
+    <t>Comment t'as pu nous faire ça ?</t>
+  </si>
+  <si>
+    <t>How could you do this to us?</t>
+  </si>
+  <si>
+    <t>Comment t'as pu nous la faire à l'envers ?</t>
+  </si>
+  <si>
+    <t>You did not meet our standards.</t>
+  </si>
+  <si>
+    <t>Vous n'avez pas satisfait à nos exigences.</t>
+  </si>
+  <si>
+    <t>T'étais pas à la hauteur.</t>
+  </si>
+  <si>
+    <t>Vous n'avez pas répondu à nos attentes.</t>
+  </si>
+  <si>
+    <t>Vous ne correspondez pas aux standards attendus.</t>
+  </si>
+  <si>
+    <t>T'as pas le niveau.</t>
+  </si>
+  <si>
+    <t>What do you mean ?</t>
+  </si>
+  <si>
+    <t>Pourriez-vous préciser le sens de votre propos ?</t>
+  </si>
+  <si>
+    <t>Qu'est-ce que vous voulez dire ?</t>
+  </si>
+  <si>
+    <t>Qu'est-ce que tu veux dire ?</t>
+  </si>
+  <si>
+    <t>Tu racontes quoi, là ?</t>
+  </si>
+  <si>
+    <t>Que souhaitez-vous dire exactement ?</t>
   </si>
 </sst>
 </file>
@@ -535,12 +661,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" customWidth="1"/>
-    <col min="3" max="3" width="55.90625" customWidth="1"/>
+    <col min="2" max="2" width="41.7265625" customWidth="1"/>
+    <col min="3" max="3" width="77.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -939,6 +1065,391 @@
         <v>46</v>
       </c>
     </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D98F229-3BEE-4FF7-9C15-8EA461696008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464173DE-3981-4C15-83D7-B50AAB647DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="146">
   <si>
     <t>register</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Je t'kiffe.</t>
   </si>
   <si>
-    <t>Je tiens énormément à toi.</t>
-  </si>
-  <si>
     <t>Je t'aime.</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>Comment t'as pu nous faire ça ?</t>
   </si>
   <si>
-    <t>How could you do this to us?</t>
-  </si>
-  <si>
     <t>Comment t'as pu nous la faire à l'envers ?</t>
   </si>
   <si>
@@ -310,6 +304,174 @@
   </si>
   <si>
     <t>Que souhaitez-vous dire exactement ?</t>
+  </si>
+  <si>
+    <t>J't'aime.</t>
+  </si>
+  <si>
+    <t>Why were you so late today ?</t>
+  </si>
+  <si>
+    <t>How could you do this to us ?</t>
+  </si>
+  <si>
+    <t>Pourriez-vous justifier votre retard important aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>Pourquoi étiez-vous si en retard aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>Comment expliquez-vous votre retard d'aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>C'était quoi ce retard de ouf aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>Pourquoi t'es arrivé si tard aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>Elle ressemble beaucoup à votre mère.</t>
+  </si>
+  <si>
+    <t>Elle présente une grande ressemblance avec votre mère.</t>
+  </si>
+  <si>
+    <t>Il est constaté qu'elle présente une forte ressemblance avec votre mère.</t>
+  </si>
+  <si>
+    <t>Elle ressemble vachement à ta mère.</t>
+  </si>
+  <si>
+    <t>Elle a grave la tête de ta mère.</t>
+  </si>
+  <si>
+    <t>She looks a lot like your mom.</t>
+  </si>
+  <si>
+    <t>See you tomorrow !</t>
+  </si>
+  <si>
+    <t>Nous vous donnons rendez-vous demain.</t>
+  </si>
+  <si>
+    <t>Au plaisir de vous revoir demain.</t>
+  </si>
+  <si>
+    <t>À d'main !</t>
+  </si>
+  <si>
+    <t>À demain !</t>
+  </si>
+  <si>
+    <t>On s'capte demain !</t>
+  </si>
+  <si>
+    <t>Can you send me the link ?</t>
+  </si>
+  <si>
+    <t>Nous vous prions de bien vouloir nous transmettre le lien concerné.</t>
+  </si>
+  <si>
+    <t>Pourriez-vous m'envoyer le lien, s'il vous plaît ?</t>
+  </si>
+  <si>
+    <t>Pouvez-vous m'envoyer le lien ?</t>
+  </si>
+  <si>
+    <t>Tu peux me passer le lien ?</t>
+  </si>
+  <si>
+    <t>File-moi le lien !</t>
+  </si>
+  <si>
+    <t>Make this make sense.</t>
+  </si>
+  <si>
+    <t>Explique-moi ce bordel.</t>
+  </si>
+  <si>
+    <t>Nous vous prions de bien vouloir apporter des précisions afin de clarifier cette situation.</t>
+  </si>
+  <si>
+    <t>Pourriez-vous m'aider à comprendre cela ?</t>
+  </si>
+  <si>
+    <t>Pouvez-vous m'expliquer cela ?</t>
+  </si>
+  <si>
+    <t>Fais-moi comprendre.</t>
+  </si>
+  <si>
+    <t>What is the purpose of life ?</t>
+  </si>
+  <si>
+    <t>Quelle est la finalité de l'existence humaine ?</t>
+  </si>
+  <si>
+    <t>Quel est le sens de la vie ?</t>
+  </si>
+  <si>
+    <t>C'est quoi, le but de la vie ?</t>
+  </si>
+  <si>
+    <t>À quoi ça rime, la vie ?</t>
+  </si>
+  <si>
+    <t>Quel est, selon vous, le sens de l'existence ?</t>
+  </si>
+  <si>
+    <t>Your father was just in an accident. I'm heading to the hospital right now.</t>
+  </si>
+  <si>
+    <t>Votre père vient d'être victime d'un accident. Je me rends immédiatement à l'hôpital.</t>
+  </si>
+  <si>
+    <t>Votre père vient d'avoir un accident. Je me rends à l'hôpital immédiatement.</t>
+  </si>
+  <si>
+    <t>Votre père a été victime d'un accident. Je me rends immédiatement à l'établissement hospitalier afin de le rejoindre.</t>
+  </si>
+  <si>
+    <t>Ton père vient d'avoir un accident. Je vais à l'hôpital tout de suite.</t>
+  </si>
+  <si>
+    <t>Ton daron vient d'avoir un accident. J'fonce à l'hosto.</t>
+  </si>
+  <si>
+    <t>The weather was not ideal. They had to cancel it.</t>
+  </si>
+  <si>
+    <t>Le temps n'était pas idéal. Ils ont dû annuler.</t>
+  </si>
+  <si>
+    <t>Les conditions météorologiques n'étaient pas favorables. Ils ont donc été contraints d'annuler.</t>
+  </si>
+  <si>
+    <t>En raison de conditions météorologiques défavorables, l'événement a dû être annulé.</t>
+  </si>
+  <si>
+    <t>Vu le temps qu'il faisait, ils ont dû annuler.</t>
+  </si>
+  <si>
+    <t>Avec un temps pareil, c'était mort.</t>
+  </si>
+  <si>
+    <t>It's been two years. What should I do ?</t>
+  </si>
+  <si>
+    <t>Deux années se sont écoulées. Quelles démarches me recommandez-vous d'entreprendre ?</t>
+  </si>
+  <si>
+    <t>Ça fait deux ans. Qu'est-ce que je suis censé faire ?</t>
+  </si>
+  <si>
+    <t>Cela fait deux ans. Que devrais-je faire ?</t>
+  </si>
+  <si>
+    <t>Ça fait deux piges. J'fais quoi, maintenant ?</t>
+  </si>
+  <si>
+    <t>Cela fait maintenant deux ans. Que devrais-je faire à présent ?</t>
   </si>
 </sst>
 </file>
@@ -661,12 +823,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="41.7265625" customWidth="1"/>
-    <col min="3" max="3" width="77.453125" customWidth="1"/>
+    <col min="2" max="2" width="68.453125" customWidth="1"/>
+    <col min="3" max="3" width="101.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -682,10 +844,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -693,761 +855,1256 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
         <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
         <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
         <v>44</v>
-      </c>
-      <c r="C32" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
         <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
         <v>62</v>
-      </c>
-      <c r="C50" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" t="s">
         <v>80</v>
-      </c>
-      <c r="C63" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" t="s">
         <v>86</v>
-      </c>
-      <c r="C69" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>87</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>91</v>
+      </c>
+      <c r="C72" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" t="s">
+        <v>103</v>
+      </c>
+      <c r="C77" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" t="s">
+        <v>103</v>
+      </c>
+      <c r="C78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" t="s">
+        <v>103</v>
+      </c>
+      <c r="C79" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>103</v>
+      </c>
+      <c r="C80" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>103</v>
+      </c>
+      <c r="C81" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
+        <v>104</v>
+      </c>
+      <c r="C82" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" t="s">
+        <v>110</v>
+      </c>
+      <c r="C87" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>110</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>110</v>
+      </c>
+      <c r="C89" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" t="s">
+        <v>116</v>
+      </c>
+      <c r="C92" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" t="s">
+        <v>116</v>
+      </c>
+      <c r="C93" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>10</v>
+      </c>
+      <c r="B94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" t="s">
+        <v>122</v>
+      </c>
+      <c r="C98" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" t="s">
+        <v>122</v>
+      </c>
+      <c r="C99" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C100" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>122</v>
+      </c>
+      <c r="C101" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>128</v>
+      </c>
+      <c r="C102" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s">
+        <v>128</v>
+      </c>
+      <c r="C103" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>10</v>
+      </c>
+      <c r="B104" t="s">
+        <v>128</v>
+      </c>
+      <c r="C104" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
+        <v>128</v>
+      </c>
+      <c r="C106" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" t="s">
+        <v>134</v>
+      </c>
+      <c r="C108" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>10</v>
+      </c>
+      <c r="B109" t="s">
+        <v>134</v>
+      </c>
+      <c r="C109" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" t="s">
+        <v>134</v>
+      </c>
+      <c r="C110" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>134</v>
+      </c>
+      <c r="C111" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" t="s">
+        <v>140</v>
+      </c>
+      <c r="C112" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>140</v>
+      </c>
+      <c r="C113" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+      <c r="B114" t="s">
+        <v>140</v>
+      </c>
+      <c r="C114" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116" t="s">
+        <v>140</v>
+      </c>
+      <c r="C116" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464173DE-3981-4C15-83D7-B50AAB647DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96B6842-64B9-45B0-892B-9D6D60C1DA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="182">
   <si>
     <t>register</t>
   </si>
@@ -472,6 +472,114 @@
   </si>
   <si>
     <t>Cela fait maintenant deux ans. Que devrais-je faire à présent ?</t>
+  </si>
+  <si>
+    <t>Cette situation ne saurait être acceptée. Une solution alternative doit être envisagée.</t>
+  </si>
+  <si>
+    <t>This is unacceptable. There has to be another way.</t>
+  </si>
+  <si>
+    <t>Cette situation est inacceptable. Il doit exister une autre solution.</t>
+  </si>
+  <si>
+    <t>Ceci est inacceptable. Il doit y avoir une autre solution.</t>
+  </si>
+  <si>
+    <t>C'est pas acceptable. Il doit bien y avoir une autre solution.</t>
+  </si>
+  <si>
+    <t>C'est abusé. Y a bien une autre solution.</t>
+  </si>
+  <si>
+    <t>Je souhaite rentrer à mon domicile. Cette situation ne correspond pas à mes attentes.</t>
+  </si>
+  <si>
+    <t>J'aimerais rentrer chez moi. Je ne pense pas que cela me convienne.</t>
+  </si>
+  <si>
+    <t>Je veux rentrer chez moi. Ce n'est vraiment pas pour moi.</t>
+  </si>
+  <si>
+    <t>J'ai envie de rentrer chez moi. Franchement, c'est pas pour moi.</t>
+  </si>
+  <si>
+    <t>J'me casse. C'est pas mon délire.</t>
+  </si>
+  <si>
+    <t>I want to go home. This really isn't for me.</t>
+  </si>
+  <si>
+    <t>Did you get a text from her ? What did she say ?</t>
+  </si>
+  <si>
+    <t>Avez-vous reçu un message de sa part ? Pourriez-vous en communiquer le contenu ?</t>
+  </si>
+  <si>
+    <t>T'as eu un texto d'elle ? Elle a dit quoi ?</t>
+  </si>
+  <si>
+    <t>Elle t'a envoyé un texto ? Elle a raconté quoi ?</t>
+  </si>
+  <si>
+    <t>Elle t'a envoyé un message ? Qu'est-ce qu'elle t'a dit ?</t>
+  </si>
+  <si>
+    <t>Vous a-t-elle envoyé un message ? Que vous a-t-elle dit ?</t>
+  </si>
+  <si>
+    <t>Êtes-vous en mesure de nager ? En ce qui me concerne, je n'en suis pas capable.</t>
+  </si>
+  <si>
+    <t>Savez-vous nager ? Pour ma part, ce n'est pas le cas.</t>
+  </si>
+  <si>
+    <t>Savez-vous nager ? Moi, non.</t>
+  </si>
+  <si>
+    <t>Tu sais nager ? Moi, non.</t>
+  </si>
+  <si>
+    <t>Tu sais nager, toi ? Moi, que dalle.</t>
+  </si>
+  <si>
+    <t>Do you know how to swim ? I don't.</t>
+  </si>
+  <si>
+    <t>Is there anything I can do for you ? I can help.</t>
+  </si>
+  <si>
+    <t>Nous restons à votre disposition si vous avez besoin d'une quelconque assistance.</t>
+  </si>
+  <si>
+    <t>Y a-t-il quelque chose que je puisse faire pour vous ? Je peux vous aider.</t>
+  </si>
+  <si>
+    <t>Y a quelque chose que je peux faire pour toi ? Je peux t'aider.</t>
+  </si>
+  <si>
+    <t>Y a-t-il quoi que ce soit que je puisse faire pour vous ? Je suis à votre disposition.</t>
+  </si>
+  <si>
+    <t>T'as besoin d'un coup de main ? J'suis là.</t>
+  </si>
+  <si>
+    <t>Il subsiste des réserves quant à la pertinence de cette proposition. Une alternative plus appropriée pourrait-elle être envisagée ?</t>
+  </si>
+  <si>
+    <t>I don't know if this is a good idea. Do you have a better one ?</t>
+  </si>
+  <si>
+    <t>Je ne sais pas si c'est une bonne idée. Avez-vous une meilleure proposition ?</t>
+  </si>
+  <si>
+    <t>Je sais pas si c'est une bonne idée. T'as une autre idée ?</t>
+  </si>
+  <si>
+    <t>J'le sens moyen, ce coup-là. T'as pas mieux ?</t>
+  </si>
+  <si>
+    <t>Je doute que cette solution soit la plus appropriée. Auriez-vous une alternative à suggérer ?</t>
   </si>
 </sst>
 </file>
@@ -823,12 +931,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="68.453125" customWidth="1"/>
-    <col min="3" max="3" width="101.08984375" customWidth="1"/>
+    <col min="2" max="2" width="64.453125" customWidth="1"/>
+    <col min="3" max="3" width="110.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -847,10 +955,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -858,10 +966,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -869,10 +977,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -880,10 +988,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -891,10 +999,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -902,10 +1010,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -913,10 +1021,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -924,10 +1032,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -935,10 +1043,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -946,10 +1054,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -2105,6 +2213,336 @@
       </c>
       <c r="C116" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>147</v>
+      </c>
+      <c r="C117" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>147</v>
+      </c>
+      <c r="C118" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>10</v>
+      </c>
+      <c r="B119" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" t="s">
+        <v>147</v>
+      </c>
+      <c r="C120" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" t="s">
+        <v>147</v>
+      </c>
+      <c r="C121" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" t="s">
+        <v>157</v>
+      </c>
+      <c r="C122" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123" t="s">
+        <v>157</v>
+      </c>
+      <c r="C123" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B124" t="s">
+        <v>157</v>
+      </c>
+      <c r="C124" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" t="s">
+        <v>157</v>
+      </c>
+      <c r="C125" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" t="s">
+        <v>157</v>
+      </c>
+      <c r="C126" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" t="s">
+        <v>158</v>
+      </c>
+      <c r="C127" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" t="s">
+        <v>158</v>
+      </c>
+      <c r="C128" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B129" t="s">
+        <v>158</v>
+      </c>
+      <c r="C129" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" t="s">
+        <v>158</v>
+      </c>
+      <c r="C130" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>158</v>
+      </c>
+      <c r="C131" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" t="s">
+        <v>169</v>
+      </c>
+      <c r="C132" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" t="s">
+        <v>169</v>
+      </c>
+      <c r="C133" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" t="s">
+        <v>169</v>
+      </c>
+      <c r="C134" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" t="s">
+        <v>169</v>
+      </c>
+      <c r="C135" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" t="s">
+        <v>169</v>
+      </c>
+      <c r="C136" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" t="s">
+        <v>170</v>
+      </c>
+      <c r="C137" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
+        <v>170</v>
+      </c>
+      <c r="C138" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" t="s">
+        <v>170</v>
+      </c>
+      <c r="C139" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" t="s">
+        <v>170</v>
+      </c>
+      <c r="C140" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s">
+        <v>170</v>
+      </c>
+      <c r="C141" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" t="s">
+        <v>177</v>
+      </c>
+      <c r="C142" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" t="s">
+        <v>177</v>
+      </c>
+      <c r="C143" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B144" t="s">
+        <v>177</v>
+      </c>
+      <c r="C144" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" t="s">
+        <v>177</v>
+      </c>
+      <c r="C145" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>177</v>
+      </c>
+      <c r="C146" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96B6842-64B9-45B0-892B-9D6D60C1DA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99609F6C-22D2-41C4-8A41-C54B5F6C92B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="200">
   <si>
     <t>register</t>
   </si>
@@ -580,6 +580,60 @@
   </si>
   <si>
     <t>Je doute que cette solution soit la plus appropriée. Auriez-vous une alternative à suggérer ?</t>
+  </si>
+  <si>
+    <t>What do you feel like having for dinner ? Anything good around here ?</t>
+  </si>
+  <si>
+    <t>Quel type de repas souhaiteriez-vous prendre ce soir ? Pourriez-vous recommander un établissement de restauration à proximité ?</t>
+  </si>
+  <si>
+    <t>Qu'auriez-vous envie de dîner ce soir ? Connaissez-vous un bon restaurant dans les environs ?</t>
+  </si>
+  <si>
+    <t>Qu'avez-vous envie de manger ce soir ? Y a-t-il un bon restaurant dans les environs ?</t>
+  </si>
+  <si>
+    <t>Ça te dit quoi pour le dîner ? Y a un bon resto dans le coin ?</t>
+  </si>
+  <si>
+    <t>Ça te chauffe quoi pour ce soir ? Y a un bon spot où bouffer dans l'coin ?</t>
+  </si>
+  <si>
+    <t>Vous êtes-vous déjà fait licencier juste avant de devoir payer votre loyer ? Ce n'est vraiment pas agréable.</t>
+  </si>
+  <si>
+    <t>Vous est-il déjà arrivé de faire l'objet d'un licenciement peu avant l'échéance de votre loyer ? Une telle situation est particulièrement difficile à vivre.</t>
+  </si>
+  <si>
+    <t>Have you ever been fired right before rent's due ? It's not fun.</t>
+  </si>
+  <si>
+    <t>Tu t'es déjà fait licencier juste avant de payer ton loyer ? C'est vraiment pas drôle.</t>
+  </si>
+  <si>
+    <t>Avez-vous déjà perdu votre emploi juste avant l'échéance de votre loyer ? C'est une épreuve particulièrement difficile.</t>
+  </si>
+  <si>
+    <t>Tu t'es déjà fait tej juste avant de payer ton loyer ? C'est vraiment la merde.</t>
+  </si>
+  <si>
+    <t>Do you speak English ? I don't understand a word you're saying.</t>
+  </si>
+  <si>
+    <t>Parlez-vous anglais ? Je ne suis pas en mesure de comprendre vos propos.</t>
+  </si>
+  <si>
+    <t>Parlez-vous anglais ? Je ne parviens pas à comprendre ce que vous dites.</t>
+  </si>
+  <si>
+    <t>Parlez-vous anglais ? Je ne comprends pas un mot de ce que vous dites.</t>
+  </si>
+  <si>
+    <t>Tu parles anglais ? Je comprends pas un mot de ce que tu dis.</t>
+  </si>
+  <si>
+    <t>Tu parles anglais ? J'pige que dalle à c'que tu racontes.</t>
   </si>
 </sst>
 </file>
@@ -931,12 +985,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
     <col min="2" max="2" width="64.453125" customWidth="1"/>
-    <col min="3" max="3" width="110.453125" customWidth="1"/>
+    <col min="3" max="3" width="125.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2545,6 +2599,171 @@
         <v>176</v>
       </c>
     </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>182</v>
+      </c>
+      <c r="C147" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" t="s">
+        <v>182</v>
+      </c>
+      <c r="C148" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>10</v>
+      </c>
+      <c r="B149" t="s">
+        <v>182</v>
+      </c>
+      <c r="C149" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" t="s">
+        <v>182</v>
+      </c>
+      <c r="C150" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>12</v>
+      </c>
+      <c r="B151" t="s">
+        <v>182</v>
+      </c>
+      <c r="C151" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>190</v>
+      </c>
+      <c r="C152" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" t="s">
+        <v>190</v>
+      </c>
+      <c r="C153" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>10</v>
+      </c>
+      <c r="B154" t="s">
+        <v>190</v>
+      </c>
+      <c r="C154" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" t="s">
+        <v>190</v>
+      </c>
+      <c r="C155" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B156" t="s">
+        <v>190</v>
+      </c>
+      <c r="C156" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>194</v>
+      </c>
+      <c r="C157" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s">
+        <v>194</v>
+      </c>
+      <c r="C158" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>10</v>
+      </c>
+      <c r="B159" t="s">
+        <v>194</v>
+      </c>
+      <c r="C159" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" t="s">
+        <v>194</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>12</v>
+      </c>
+      <c r="B161" t="s">
+        <v>194</v>
+      </c>
+      <c r="C161" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99609F6C-22D2-41C4-8A41-C54B5F6C92B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD99202-8116-40D3-9B35-ECA72664C11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="224">
   <si>
     <t>register</t>
   </si>
@@ -634,6 +634,78 @@
   </si>
   <si>
     <t>Tu parles anglais ? J'pige que dalle à c'que tu racontes.</t>
+  </si>
+  <si>
+    <t>Life isn't that complicated. You just think too much.</t>
+  </si>
+  <si>
+    <t>La vie ne présente pas une telle complexité. Une tendance à la suranalyse semble être en cause.</t>
+  </si>
+  <si>
+    <t>La vie n'est pas aussi compliquée qu'elle en a l'air. Vous avez tendance à trop réfléchir.</t>
+  </si>
+  <si>
+    <t>La vie n'est pas si compliquée. Vous réfléchissez trop.</t>
+  </si>
+  <si>
+    <t>La vie est pas si compliquée. Tu réfléchis trop.</t>
+  </si>
+  <si>
+    <t>La vie, c'est pas si ouf. C'est toi qui t'prends la tête pour rien.</t>
+  </si>
+  <si>
+    <t>Is there a problem ? What were they talking about ?</t>
+  </si>
+  <si>
+    <t>Un problème est-il à signaler ? Quel était l'objet de leur conversation ?</t>
+  </si>
+  <si>
+    <t>Y a-t-il un problème ? De quoi s'entretenaient-ils ?</t>
+  </si>
+  <si>
+    <t>Y a-t-il un problème ? De quoi parlaient-ils ?</t>
+  </si>
+  <si>
+    <t>Y a un problème ? De quoi ils parlaient ?</t>
+  </si>
+  <si>
+    <t>Ça va pas ou quoi ? Ils se racontaient quoi ?</t>
+  </si>
+  <si>
+    <t>This isn't right. Someone should get sued over this.</t>
+  </si>
+  <si>
+    <t>Cette situation est inacceptable. Il conviendrait d'engager des poursuites judiciaires à l'encontre des personnes responsables.</t>
+  </si>
+  <si>
+    <t>Ce n'est pas acceptable. Quelqu'un devrait être poursuivi en justice pour cela.</t>
+  </si>
+  <si>
+    <t>C'est n'importe quoi. Y en a un qui mérite de finir au tribunal.</t>
+  </si>
+  <si>
+    <t>Une telle situation est inacceptable. Les responsables devraient répondre de leurs actes devant la justice.</t>
+  </si>
+  <si>
+    <t>Ça va pas du tout. Quelqu'un devrait répondre de ça devant la justice.</t>
+  </si>
+  <si>
+    <t>It's gonna be a 20-minute wait. Is that okay ?</t>
+  </si>
+  <si>
+    <t>Le délai d'attente est estimé à une vingtaine de minutes. Nous vous remercions de votre compréhension.</t>
+  </si>
+  <si>
+    <t>Le temps d'attente sera d'environ vingt minutes. Est-ce que cela vous conviendrait ?</t>
+  </si>
+  <si>
+    <t>Il y aura environ vingt minutes d'attente. Est-ce que cela vous convient ?</t>
+  </si>
+  <si>
+    <t>On en a pour vingt minutes à peu près. Ça te va ?</t>
+  </si>
+  <si>
+    <t>Y a vingt minutes de queue. Ça te gêne ?</t>
   </si>
 </sst>
 </file>
@@ -985,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
@@ -2764,6 +2836,226 @@
         <v>195</v>
       </c>
     </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>200</v>
+      </c>
+      <c r="C162" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" t="s">
+        <v>200</v>
+      </c>
+      <c r="C163" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164" t="s">
+        <v>200</v>
+      </c>
+      <c r="C164" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>11</v>
+      </c>
+      <c r="B165" t="s">
+        <v>200</v>
+      </c>
+      <c r="C165" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>12</v>
+      </c>
+      <c r="B166" t="s">
+        <v>200</v>
+      </c>
+      <c r="C166" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>206</v>
+      </c>
+      <c r="C167" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" t="s">
+        <v>206</v>
+      </c>
+      <c r="C168" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169" t="s">
+        <v>206</v>
+      </c>
+      <c r="C169" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" t="s">
+        <v>206</v>
+      </c>
+      <c r="C170" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>12</v>
+      </c>
+      <c r="B171" t="s">
+        <v>206</v>
+      </c>
+      <c r="C171" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>212</v>
+      </c>
+      <c r="C172" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" t="s">
+        <v>212</v>
+      </c>
+      <c r="C173" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174" t="s">
+        <v>212</v>
+      </c>
+      <c r="C174" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" t="s">
+        <v>212</v>
+      </c>
+      <c r="C175" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B176" t="s">
+        <v>212</v>
+      </c>
+      <c r="C176" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>218</v>
+      </c>
+      <c r="C177" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>218</v>
+      </c>
+      <c r="C178" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>218</v>
+      </c>
+      <c r="C179" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>218</v>
+      </c>
+      <c r="C180" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>12</v>
+      </c>
+      <c r="B181" t="s">
+        <v>218</v>
+      </c>
+      <c r="C181" t="s">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD99202-8116-40D3-9B35-ECA72664C11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5681989B-DD91-487A-9306-657E9B14B1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="272">
   <si>
     <t>register</t>
   </si>
@@ -706,6 +706,150 @@
   </si>
   <si>
     <t>Y a vingt minutes de queue. Ça te gêne ?</t>
+  </si>
+  <si>
+    <t>Your grandparents aren't coming ? Why ?</t>
+  </si>
+  <si>
+    <t>Vos grands-parents ne seront-ils pas présents ? Pourriez-vous en préciser la raison ?</t>
+  </si>
+  <si>
+    <t>Vos grands-parents ne seront-ils pas des nôtres ? Pour quelle raison ?</t>
+  </si>
+  <si>
+    <t>Vos grands-parents ne viennent-ils pas ? Pourquoi ?</t>
+  </si>
+  <si>
+    <t>Tes grands-parents viennent pas ? Pourquoi ?</t>
+  </si>
+  <si>
+    <t>Tes grands-parents sont pas là ? Qu'est-ce qui se passe ?</t>
+  </si>
+  <si>
+    <t>Just calm down. Breathe slowly.</t>
+  </si>
+  <si>
+    <t>Nous vous invitons à garder votre calme et à respirer lentement.</t>
+  </si>
+  <si>
+    <t>Je vous en prie, essayez de rester calme. Respirez lentement.</t>
+  </si>
+  <si>
+    <t>Calmez-vous. Respirez lentement.</t>
+  </si>
+  <si>
+    <t>Calme-toi. Respire doucement.</t>
+  </si>
+  <si>
+    <t>Vas-y, pose-toi. Respire tranquille.</t>
+  </si>
+  <si>
+    <t>The cheese will be served when I want it served, and I want it served now.</t>
+  </si>
+  <si>
+    <t>Le fromage sera servi au moment que je jugerai opportun, et je souhaite qu'il le soit sans délai.</t>
+  </si>
+  <si>
+    <t>Le fromage sera servi lorsque je le déciderai, et je le veux servi immédiatement.</t>
+  </si>
+  <si>
+    <t>Le fromage sera servi quand je l'aurai décidé, et je le veux tout de suite.</t>
+  </si>
+  <si>
+    <t>Le fromage sera servi conformément aux instructions en vigueur. En l'espèce, il est demandé qu'il soit servi sans délai.</t>
+  </si>
+  <si>
+    <t>Le fromage, tu l'amènes quand j'dis. Et j'dis tout de suite.</t>
+  </si>
+  <si>
+    <t>I want him dead. You know what to do.</t>
+  </si>
+  <si>
+    <t>Il est demandé que cet individu soit neutralisé. Vous connaissez la procédure à suivre.</t>
+  </si>
+  <si>
+    <t>Je veux qu'il soit éliminé. Vous savez ce qu'il vous reste à faire.</t>
+  </si>
+  <si>
+    <t>Je le veux mort. Vous savez ce qu'il faut faire.</t>
+  </si>
+  <si>
+    <t>Je le veux mort. Tu sais ce qu'il faut faire.</t>
+  </si>
+  <si>
+    <t>J'veux qu'il disparaisse. T'as capté c'qu'il faut faire.</t>
+  </si>
+  <si>
+    <t>Where were you ? We were all waiting for you !</t>
+  </si>
+  <si>
+    <t>Où étiez-vous ? L'ensemble des personnes présentes était dans l'attente de votre arrivée.</t>
+  </si>
+  <si>
+    <t>Où étiez-vous ? Nous vous attendions tous !</t>
+  </si>
+  <si>
+    <t>T'étais où ? On t'attendait tous !</t>
+  </si>
+  <si>
+    <t>Où donc étiez-vous ? Nous vous attendions tous.</t>
+  </si>
+  <si>
+    <t>T'as foutu quoi ? On poireautait tous à t'attendre !</t>
+  </si>
+  <si>
+    <t>She's been around since the company's founding.</t>
+  </si>
+  <si>
+    <t>Elle est employée au sein de l'entreprise depuis sa création.</t>
+  </si>
+  <si>
+    <t>Elle fait partie de l'entreprise depuis sa fondation.</t>
+  </si>
+  <si>
+    <t>Elle est dans l'entreprise depuis sa création.</t>
+  </si>
+  <si>
+    <t>Elle est là depuis la création de la boîte.</t>
+  </si>
+  <si>
+    <t>Elle est là depuis que la boîte existe.</t>
+  </si>
+  <si>
+    <t>How many incidents are we going to have before the authorities do something ?</t>
+  </si>
+  <si>
+    <t>Combien d'incidents supplémentaires seront nécessaires avant que les autorités mettent en œuvre les mesures appropriées ?</t>
+  </si>
+  <si>
+    <t>Combien d'incidents devront encore se produire avant que les autorités prennent des mesures ?</t>
+  </si>
+  <si>
+    <t>Combien d'incidents faudra-t-il encore avant que les autorités interviennent ?</t>
+  </si>
+  <si>
+    <t>Il va falloir combien d'incidents avant que les autorités réagissent ?</t>
+  </si>
+  <si>
+    <t>Combien de bordels faudra encore avant qu'ils bougent enfin ?</t>
+  </si>
+  <si>
+    <t>Get this done by tonight so that they can start working on it tomorrow morning.</t>
+  </si>
+  <si>
+    <t>Il est demandé que ce travail soit finalisé avant la fin de la journée afin de permettre le démarrage des opérations demain matin.</t>
+  </si>
+  <si>
+    <t>Je vous prie de finaliser ce dossier d'ici ce soir afin qu'ils puissent entamer les travaux demain matin.</t>
+  </si>
+  <si>
+    <t>Terminez cela d'ici ce soir afin qu'ils puissent commencer à y travailler demain matin.</t>
+  </si>
+  <si>
+    <t>Faut que ce soit prêt ce soir, comme ça ils pourront commencer demain matin.</t>
+  </si>
+  <si>
+    <t>Faut que ça soit plié ce soir, qu'ils s'y mettent demain matin.</t>
   </si>
 </sst>
 </file>
@@ -1057,11 +1201,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C221"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="64.453125" customWidth="1"/>
+    <col min="2" max="2" width="70.7265625" customWidth="1"/>
     <col min="3" max="3" width="125.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3056,6 +3200,446 @@
         <v>219</v>
       </c>
     </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>224</v>
+      </c>
+      <c r="C182" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" t="s">
+        <v>224</v>
+      </c>
+      <c r="C183" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184" t="s">
+        <v>224</v>
+      </c>
+      <c r="C184" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" t="s">
+        <v>224</v>
+      </c>
+      <c r="C185" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>12</v>
+      </c>
+      <c r="B186" t="s">
+        <v>224</v>
+      </c>
+      <c r="C186" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
+        <v>230</v>
+      </c>
+      <c r="C187" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188" t="s">
+        <v>230</v>
+      </c>
+      <c r="C188" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>10</v>
+      </c>
+      <c r="B189" t="s">
+        <v>230</v>
+      </c>
+      <c r="C189" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" t="s">
+        <v>230</v>
+      </c>
+      <c r="C190" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>230</v>
+      </c>
+      <c r="C191" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" t="s">
+        <v>242</v>
+      </c>
+      <c r="C192" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" t="s">
+        <v>242</v>
+      </c>
+      <c r="C193" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B194" t="s">
+        <v>242</v>
+      </c>
+      <c r="C194" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" t="s">
+        <v>242</v>
+      </c>
+      <c r="C195" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>12</v>
+      </c>
+      <c r="B196" t="s">
+        <v>242</v>
+      </c>
+      <c r="C196" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" t="s">
+        <v>248</v>
+      </c>
+      <c r="C197" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" t="s">
+        <v>248</v>
+      </c>
+      <c r="C198" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>10</v>
+      </c>
+      <c r="B199" t="s">
+        <v>248</v>
+      </c>
+      <c r="C199" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>11</v>
+      </c>
+      <c r="B200" t="s">
+        <v>248</v>
+      </c>
+      <c r="C200" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>12</v>
+      </c>
+      <c r="B201" t="s">
+        <v>248</v>
+      </c>
+      <c r="C201" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202" t="s">
+        <v>236</v>
+      </c>
+      <c r="C202" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" t="s">
+        <v>236</v>
+      </c>
+      <c r="C203" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204" t="s">
+        <v>236</v>
+      </c>
+      <c r="C204" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>11</v>
+      </c>
+      <c r="B205" t="s">
+        <v>236</v>
+      </c>
+      <c r="C205" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>12</v>
+      </c>
+      <c r="B206" t="s">
+        <v>236</v>
+      </c>
+      <c r="C206" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" t="s">
+        <v>254</v>
+      </c>
+      <c r="C207" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" t="s">
+        <v>254</v>
+      </c>
+      <c r="C208" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>10</v>
+      </c>
+      <c r="B209" t="s">
+        <v>254</v>
+      </c>
+      <c r="C209" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>11</v>
+      </c>
+      <c r="B210" t="s">
+        <v>254</v>
+      </c>
+      <c r="C210" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>12</v>
+      </c>
+      <c r="B211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C211" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" t="s">
+        <v>260</v>
+      </c>
+      <c r="C212" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" t="s">
+        <v>260</v>
+      </c>
+      <c r="C213" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>10</v>
+      </c>
+      <c r="B214" t="s">
+        <v>260</v>
+      </c>
+      <c r="C214" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>11</v>
+      </c>
+      <c r="B215" t="s">
+        <v>260</v>
+      </c>
+      <c r="C215" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>260</v>
+      </c>
+      <c r="C216" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>8</v>
+      </c>
+      <c r="B217" t="s">
+        <v>266</v>
+      </c>
+      <c r="C217" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" t="s">
+        <v>266</v>
+      </c>
+      <c r="C218" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>10</v>
+      </c>
+      <c r="B219" t="s">
+        <v>266</v>
+      </c>
+      <c r="C219" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>11</v>
+      </c>
+      <c r="B220" t="s">
+        <v>266</v>
+      </c>
+      <c r="C220" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221" t="s">
+        <v>266</v>
+      </c>
+      <c r="C221" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5681989B-DD91-487A-9306-657E9B14B1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C182030C-CC24-4107-A406-77D51AE98C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="296">
   <si>
     <t>register</t>
   </si>
@@ -850,6 +850,78 @@
   </si>
   <si>
     <t>Faut que ça soit plié ce soir, qu'ils s'y mettent demain matin.</t>
+  </si>
+  <si>
+    <t>Here you are complaining when others are already out there solving the problem.</t>
+  </si>
+  <si>
+    <t>Vous vous plaignez alors que d'autres sont déjà à l'œuvre pour résoudre le problème.</t>
+  </si>
+  <si>
+    <t>Vous êtes là à vous plaindre alors que les autres sont déjà en train de résoudre le problème.</t>
+  </si>
+  <si>
+    <t>Toi, tu te plains alors que les autres sont déjà en train de résoudre le problème.</t>
+  </si>
+  <si>
+    <t>T'es là à brasser de l'air alors que les autres font le taf.</t>
+  </si>
+  <si>
+    <t>Alors que le problème est déjà en cours de traitement par les services compétents, vous continuez à formuler des plaintes.</t>
+  </si>
+  <si>
+    <t>Life has been so fast paced these past few days that I haven't had much time to think.</t>
+  </si>
+  <si>
+    <t>Le rythme soutenu de ces derniers jours ne m'a pas permis de consacrer le temps nécessaire à la réflexion.</t>
+  </si>
+  <si>
+    <t>Ces derniers jours ont été particulièrement intenses, au point que je n'ai guère eu le temps de prendre du recul.</t>
+  </si>
+  <si>
+    <t>Ces derniers jours ont été si chargés que je n'ai pas eu beaucoup de temps pour réfléchir.</t>
+  </si>
+  <si>
+    <t>J'ai pas arrêté ces derniers jours. J'ai à peine eu le temps de penser.</t>
+  </si>
+  <si>
+    <t>Ces derniers jours, c'était le feu. J'ai pas eu le temps de cogiter.</t>
+  </si>
+  <si>
+    <t>The higher-ups didn't like it, so this isn't going to work.</t>
+  </si>
+  <si>
+    <t>La proposition n'a pas reçu l'approbation de la direction. En conséquence, elle ne pourra pas être mise en œuvre.</t>
+  </si>
+  <si>
+    <t>La direction n'a pas apprécié, donc cela ne fonctionnera pas.</t>
+  </si>
+  <si>
+    <t>Les responsables n'ont pas aimé, donc ça ne va pas marcher.</t>
+  </si>
+  <si>
+    <t>Les boss ont pas kiffé, donc ça va pas le faire.</t>
+  </si>
+  <si>
+    <t>La direction n'a pas retenu cette proposition. Par conséquent, elle ne pourra pas être mise en œuvre.</t>
+  </si>
+  <si>
+    <t>En raison de son allergie aux produits laitiers, aucun gâteau ne pourra être servi.</t>
+  </si>
+  <si>
+    <t>Il est allergique aux produits laitiers, donc malheureusement, nous ne pouvons pas prendre de gâteau.</t>
+  </si>
+  <si>
+    <t>Il est allergique aux produits laitiers, donc malheureusement, on peut pas prendre de gâteau.</t>
+  </si>
+  <si>
+    <t>Il peut pas blairer les produits laitiers, donc c'est mort pour le gâteau.</t>
+  </si>
+  <si>
+    <t>Compte tenu de son allergie aux produits laitiers, nous devrons malheureusement renoncer au gâteau.</t>
+  </si>
+  <si>
+    <t>He's allergic to dairy, so unfortunately we can't have cake.</t>
   </si>
 </sst>
 </file>
@@ -1201,11 +1273,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C221"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="75.1796875" customWidth="1"/>
     <col min="3" max="3" width="125.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3640,6 +3712,226 @@
         <v>267</v>
       </c>
     </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222" t="s">
+        <v>272</v>
+      </c>
+      <c r="C222" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" t="s">
+        <v>272</v>
+      </c>
+      <c r="C223" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>10</v>
+      </c>
+      <c r="B224" t="s">
+        <v>272</v>
+      </c>
+      <c r="C224" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>11</v>
+      </c>
+      <c r="B225" t="s">
+        <v>272</v>
+      </c>
+      <c r="C225" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" t="s">
+        <v>272</v>
+      </c>
+      <c r="C226" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>8</v>
+      </c>
+      <c r="B227" t="s">
+        <v>278</v>
+      </c>
+      <c r="C227" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228" t="s">
+        <v>278</v>
+      </c>
+      <c r="C228" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>10</v>
+      </c>
+      <c r="B229" t="s">
+        <v>278</v>
+      </c>
+      <c r="C229" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>11</v>
+      </c>
+      <c r="B230" t="s">
+        <v>278</v>
+      </c>
+      <c r="C230" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231" t="s">
+        <v>278</v>
+      </c>
+      <c r="C231" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>8</v>
+      </c>
+      <c r="B232" t="s">
+        <v>284</v>
+      </c>
+      <c r="C232" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" t="s">
+        <v>284</v>
+      </c>
+      <c r="C233" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>10</v>
+      </c>
+      <c r="B234" t="s">
+        <v>284</v>
+      </c>
+      <c r="C234" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>11</v>
+      </c>
+      <c r="B235" t="s">
+        <v>284</v>
+      </c>
+      <c r="C235" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>284</v>
+      </c>
+      <c r="C236" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>8</v>
+      </c>
+      <c r="B237" t="s">
+        <v>295</v>
+      </c>
+      <c r="C237" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" t="s">
+        <v>295</v>
+      </c>
+      <c r="C238" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>10</v>
+      </c>
+      <c r="B239" t="s">
+        <v>295</v>
+      </c>
+      <c r="C239" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>11</v>
+      </c>
+      <c r="B240" t="s">
+        <v>295</v>
+      </c>
+      <c r="C240" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241" t="s">
+        <v>295</v>
+      </c>
+      <c r="C241" t="s">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datasets/train.xlsx
+++ b/datasets/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssvzwng\Desktop\tuouvous\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C182030C-CC24-4107-A406-77D51AE98C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64329855-8A83-43D1-88D6-B74EDCB39732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95B6576-85E5-4B51-9FB5-90017593C264}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="326">
   <si>
     <t>register</t>
   </si>
@@ -922,6 +922,96 @@
   </si>
   <si>
     <t>He's allergic to dairy, so unfortunately we can't have cake.</t>
+  </si>
+  <si>
+    <t>If nothing can be done, I'm going to have to resign.</t>
+  </si>
+  <si>
+    <t>Si rien ne peut être fait, je vais devoir démissionner.</t>
+  </si>
+  <si>
+    <t>En l'absence de toute solution, je me verrai dans l'obligation de remettre ma démission.</t>
+  </si>
+  <si>
+    <t>Si on peut rien faire, je vais devoir démissionner.</t>
+  </si>
+  <si>
+    <t>Faute de solution, je n'aurai d'autre choix que de présenter ma démission.</t>
+  </si>
+  <si>
+    <t>Si ça bouge pas, j'me casse.</t>
+  </si>
+  <si>
+    <t>I wanna leave, but I don't feel ready.</t>
+  </si>
+  <si>
+    <t>J'ai envie de partir, mais je ne me sens pas prêt.</t>
+  </si>
+  <si>
+    <t>J'aimerais partir, mais je ne me sens pas encore prêt.</t>
+  </si>
+  <si>
+    <t>À ce stade, je souhaite quitter mes fonctions, mais je ne me considère pas encore prêt à le faire.</t>
+  </si>
+  <si>
+    <t>J'ai bien envie de partir, mais je me sens pas encore prêt.</t>
+  </si>
+  <si>
+    <t>J'ai envie de me casser, mais j'me sens pas prêt.</t>
+  </si>
+  <si>
+    <t>If she's scared, we should get someone else to do the job !</t>
+  </si>
+  <si>
+    <t>Si elle n'est pas en mesure d'occuper ce poste, il conviendra de désigner une autre personne pour l'occuper.</t>
+  </si>
+  <si>
+    <t>Si elle ne se sent pas en mesure d'occuper ce poste, il serait préférable de le confier à une autre personne.</t>
+  </si>
+  <si>
+    <t>Si elle a peur, nous devrions trouver quelqu'un d'autre pour occuper ce poste.</t>
+  </si>
+  <si>
+    <t>Si elle a peur, on devrait trouver quelqu'un d'autre pour prendre le poste.</t>
+  </si>
+  <si>
+    <t>Si elle flippe, faut trouver quelqu'un d'autre pour prendre sa place !</t>
+  </si>
+  <si>
+    <t>Should we get burgers or pizzas ?</t>
+  </si>
+  <si>
+    <t>Veuillez indiquer si vous préférez que le choix se porte sur des burgers ou des pizzas.</t>
+  </si>
+  <si>
+    <t>Préféreriez-vous que nous prenions des burgers ou des pizzas ?</t>
+  </si>
+  <si>
+    <t>Est-ce qu'on prend des burgers ou des pizzas ?</t>
+  </si>
+  <si>
+    <t>On prend des burgers ou des pizzas ?</t>
+  </si>
+  <si>
+    <t>On s'fait des burgers ou des pizzas ?</t>
+  </si>
+  <si>
+    <t>I'm sorry but this isn't gonna work.</t>
+  </si>
+  <si>
+    <t>Nous sommes au regret de vous informer que cette solution ne pourra pas être mise en œuvre.</t>
+  </si>
+  <si>
+    <t>Je suis désolé, mais cela ne pourra malheureusement pas fonctionner.</t>
+  </si>
+  <si>
+    <t>Je suis désolé, mais cela ne va pas fonctionner.</t>
+  </si>
+  <si>
+    <t>Désolé, mais ça va pas marcher.</t>
+  </si>
+  <si>
+    <t>Désolé, mais ça va pas le faire.</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903655B4-DA13-47A5-888D-532BF9DF7DF6}">
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C266"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
@@ -3932,6 +4022,281 @@
         <v>290</v>
       </c>
     </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>8</v>
+      </c>
+      <c r="B242" t="s">
+        <v>296</v>
+      </c>
+      <c r="C242" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" t="s">
+        <v>296</v>
+      </c>
+      <c r="C243" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>10</v>
+      </c>
+      <c r="B244" t="s">
+        <v>296</v>
+      </c>
+      <c r="C244" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>11</v>
+      </c>
+      <c r="B245" t="s">
+        <v>296</v>
+      </c>
+      <c r="C245" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>12</v>
+      </c>
+      <c r="B246" t="s">
+        <v>296</v>
+      </c>
+      <c r="C246" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>8</v>
+      </c>
+      <c r="B247" t="s">
+        <v>302</v>
+      </c>
+      <c r="C247" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" t="s">
+        <v>302</v>
+      </c>
+      <c r="C248" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>10</v>
+      </c>
+      <c r="B249" t="s">
+        <v>302</v>
+      </c>
+      <c r="C249" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>11</v>
+      </c>
+      <c r="B250" t="s">
+        <v>302</v>
+      </c>
+      <c r="C250" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251" t="s">
+        <v>302</v>
+      </c>
+      <c r="C251" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>8</v>
+      </c>
+      <c r="B252" t="s">
+        <v>308</v>
+      </c>
+      <c r="C252" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" t="s">
+        <v>308</v>
+      </c>
+      <c r="C253" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>10</v>
+      </c>
+      <c r="B254" t="s">
+        <v>308</v>
+      </c>
+      <c r="C254" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>11</v>
+      </c>
+      <c r="B255" t="s">
+        <v>308</v>
+      </c>
+      <c r="C255" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>12</v>
+      </c>
+      <c r="B256" t="s">
+        <v>308</v>
+      </c>
+      <c r="C256" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>8</v>
+      </c>
+      <c r="B257" t="s">
+        <v>314</v>
+      </c>
+      <c r="C257" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" t="s">
+        <v>314</v>
+      </c>
+      <c r="C258" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>10</v>
+      </c>
+      <c r="B259" t="s">
+        <v>314</v>
+      </c>
+      <c r="C259" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>11</v>
+      </c>
+      <c r="B260" t="s">
+        <v>314</v>
+      </c>
+      <c r="C260" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261" t="s">
+        <v>314</v>
+      </c>
+      <c r="C261" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>8</v>
+      </c>
+      <c r="B262" t="s">
+        <v>320</v>
+      </c>
+      <c r="C262" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" t="s">
+        <v>320</v>
+      </c>
+      <c r="C263" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>10</v>
+      </c>
+      <c r="B264" t="s">
+        <v>320</v>
+      </c>
+      <c r="C264" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>11</v>
+      </c>
+      <c r="B265" t="s">
+        <v>320</v>
+      </c>
+      <c r="C265" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266" t="s">
+        <v>320</v>
+      </c>
+      <c r="C266" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
